--- a/examples_and_explanation/U-net Trial Results.xlsx
+++ b/examples_and_explanation/U-net Trial Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hankg/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B35F5B3-A2EC-A443-AF20-3B3E11D9B0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18F8D26-A900-BF44-81A9-E3C32BE28D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{073FA8C0-2077-3A48-8A5E-B44735438917}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19900" xr2:uid="{073FA8C0-2077-3A48-8A5E-B44735438917}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -100,15 +100,9 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>TRIAL STOPPED, SAME DICE ISSUES AS ABOVE</t>
-  </si>
-  <si>
     <t>NOTE: THESE 4 DICE TRIALS WERE HALTED. AFTER 30 EPOCHS, NO MASK PREDICTED, AND WILDLY ERRATIC LOSS CURVES THROUGH END OF TRIALS.</t>
   </si>
   <si>
-    <t>SC2</t>
-  </si>
-  <si>
     <t>256x256</t>
   </si>
   <si>
@@ -121,10 +115,16 @@
     <t>CONCLUSIONS</t>
   </si>
   <si>
-    <t>Accuracy peaked around 86%. Sigmoid seems to be moderately better than linear for the output activation function. Larger image size and more steps per epoch also seem to help, but this is not hard and fast. More rigorous statistical analysis, as well as more trials, would be necessary to glean more useful insights.</t>
-  </si>
-  <si>
     <t>All trials ran for 300 epochs, with early stopping and learning rate reduction. All stopped before 300 epochs (see code for ES implementation). All had same train length (number of training images), buffer size, and all non-tutorial trials had the same dropout rates (see code for specifics). All non-tutorial trials also utilized a batch normalization layer in each convolution block, while the tutorial trials did not. Some trials were full color, some were single channel.</t>
+  </si>
+  <si>
+    <t>Softmax</t>
+  </si>
+  <si>
+    <t>Accuracy peaked around 86%. Softmax seems to be moderately better than linear for the output activation function. Larger image size and more steps per epoch also seem to help, but this is not hard and fast. More rigorous statistical analysis, as well as more trials, would be necessary to glean more useful insights.</t>
+  </si>
+  <si>
+    <t>TRIAL STOPPED, SAME DICE ISSUES AS ABOVE.</t>
   </si>
 </sst>
 </file>
@@ -181,10 +181,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -515,50 +515,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="A1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -591,7 +591,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -606,10 +606,10 @@
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H6">
         <v>0.36099999999999999</v>
@@ -635,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>16</v>
@@ -664,10 +664,10 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H8">
         <v>0.48399999999999999</v>
@@ -693,10 +693,10 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H9">
         <v>0.38200000000000001</v>
@@ -722,7 +722,7 @@
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
         <v>16</v>
@@ -751,7 +751,7 @@
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
         <v>16</v>
@@ -780,10 +780,10 @@
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H12">
         <v>0.46500000000000002</v>
@@ -809,10 +809,10 @@
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H13">
         <v>0.38</v>
@@ -838,10 +838,10 @@
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H14">
         <v>0.39300000000000002</v>
@@ -867,10 +867,10 @@
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H15">
         <v>0.40500000000000003</v>
@@ -896,10 +896,10 @@
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H16">
         <v>0.40300000000000002</v>
@@ -925,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G17" t="s">
         <v>16</v>
@@ -954,10 +954,10 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H18">
         <v>0.39200000000000002</v>
@@ -986,7 +986,7 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
         <v>16</v>
@@ -1015,7 +1015,7 @@
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G21" t="s">
         <v>16</v>
@@ -1044,10 +1044,10 @@
         <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H22">
         <v>0.47899999999999998</v>
@@ -1073,10 +1073,10 @@
         <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H23">
         <v>0.49</v>
@@ -1102,7 +1102,7 @@
         <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G24" t="s">
         <v>16</v>
@@ -1131,7 +1131,7 @@
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
         <v>16</v>
@@ -1160,10 +1160,10 @@
         <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H26">
         <v>0.307</v>
@@ -1189,7 +1189,7 @@
         <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G27" t="s">
         <v>16</v>
@@ -1218,10 +1218,10 @@
         <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H28">
         <v>0.39300000000000002</v>
@@ -1247,7 +1247,7 @@
         <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G29" t="s">
         <v>16</v>
@@ -1276,7 +1276,7 @@
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G30" t="s">
         <v>16</v>
@@ -1305,7 +1305,7 @@
         <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -1334,17 +1334,17 @@
         <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
@@ -1363,15 +1363,15 @@
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -1390,15 +1390,15 @@
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
@@ -1417,15 +1417,15 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G36" t="s">
         <v>16</v>
       </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -1444,10 +1444,10 @@
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H38">
         <v>0.497</v>
@@ -1473,10 +1473,10 @@
         <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H40">
         <v>0.29899999999999999</v>
@@ -1502,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G41" t="s">
         <v>16</v>
@@ -1531,13 +1531,13 @@
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G42" t="s">
         <v>16</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -1557,10 +1557,10 @@
         <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H43">
         <v>0.36499999999999999</v>
@@ -1586,10 +1586,10 @@
         <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G44" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H44">
         <v>0.36599999999999999</v>
@@ -1600,32 +1600,32 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
